--- a/3_PPTurnover/input/dict/Dict_EF_CO2_Process.xlsx
+++ b/3_PPTurnover/input/dict/Dict_EF_CO2_Process.xlsx
@@ -5,15 +5,16 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\92978\Desktop\Unit-level-Turnover-Model-main\3_PPTurnover\input\dict\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\92978\Desktop\Unit-level-Turnover-Model\3_PPTurnover\input\dict\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BECBA5A2-3EE0-4990-AE4E-0DF14EE0D581}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E19DA2D-0CBD-4099-B371-168CA342C8FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Coal" sheetId="7" r:id="rId1"/>
+    <sheet name="Readme" sheetId="8" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>Tech</t>
   </si>
@@ -46,12 +47,64 @@
     <t>Coal</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <r>
+      <t>This file provides process-based CO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>₂</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> emission factors. In the power sector, these values are set to zero, as CO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>₂</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> emissions mainly arise from fuel combustion rather than process-related emissions.</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Unit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>t/kWh</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -73,17 +126,29 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <name val="宋体"/>
-      <charset val="134"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
-      <color indexed="8"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Cambria Math"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -121,21 +186,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -438,209 +502,232 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13EAE97E-FF76-42F8-85C8-488BC28289F4}">
-  <dimension ref="A1:AH2"/>
+  <dimension ref="A1:AI2"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.06640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="5.06640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.1328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.46484375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:35" ht="13.9" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="4">
+      <c r="B1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="3">
         <v>2022</v>
       </c>
-      <c r="D1" s="4">
+      <c r="E1" s="3">
         <v>2023</v>
       </c>
-      <c r="E1" s="4">
+      <c r="F1" s="3">
         <v>2024</v>
       </c>
-      <c r="F1" s="4">
+      <c r="G1" s="3">
         <v>2025</v>
       </c>
-      <c r="G1" s="4">
+      <c r="H1" s="3">
         <v>2026</v>
       </c>
-      <c r="H1" s="4">
+      <c r="I1" s="3">
         <v>2027</v>
       </c>
-      <c r="I1" s="4">
+      <c r="J1" s="3">
         <v>2028</v>
       </c>
-      <c r="J1" s="4">
+      <c r="K1" s="3">
         <v>2029</v>
       </c>
-      <c r="K1" s="4">
+      <c r="L1" s="3">
         <v>2030</v>
       </c>
-      <c r="L1" s="4">
+      <c r="M1" s="3">
         <v>2031</v>
       </c>
-      <c r="M1" s="4">
+      <c r="N1" s="3">
         <v>2032</v>
       </c>
-      <c r="N1" s="4">
+      <c r="O1" s="3">
         <v>2033</v>
       </c>
-      <c r="O1" s="4">
+      <c r="P1" s="3">
         <v>2034</v>
       </c>
-      <c r="P1" s="4">
+      <c r="Q1" s="3">
         <v>2035</v>
       </c>
-      <c r="Q1" s="4">
+      <c r="R1" s="3">
         <v>2036</v>
       </c>
-      <c r="R1" s="4">
+      <c r="S1" s="3">
         <v>2037</v>
       </c>
-      <c r="S1" s="4">
+      <c r="T1" s="3">
         <v>2038</v>
       </c>
-      <c r="T1" s="4">
+      <c r="U1" s="3">
         <v>2039</v>
       </c>
-      <c r="U1" s="4">
+      <c r="V1" s="3">
         <v>2040</v>
       </c>
-      <c r="V1" s="4">
+      <c r="W1" s="3">
         <v>2041</v>
       </c>
-      <c r="W1" s="4">
+      <c r="X1" s="3">
         <v>2042</v>
       </c>
-      <c r="X1" s="4">
+      <c r="Y1" s="3">
         <v>2043</v>
       </c>
-      <c r="Y1" s="4">
+      <c r="Z1" s="3">
         <v>2044</v>
       </c>
-      <c r="Z1" s="4">
+      <c r="AA1" s="3">
         <v>2045</v>
       </c>
-      <c r="AA1" s="4">
+      <c r="AB1" s="3">
         <v>2046</v>
       </c>
-      <c r="AB1" s="4">
+      <c r="AC1" s="3">
         <v>2047</v>
       </c>
-      <c r="AC1" s="4">
+      <c r="AD1" s="3">
         <v>2048</v>
       </c>
-      <c r="AD1" s="4">
+      <c r="AE1" s="3">
         <v>2049</v>
       </c>
-      <c r="AE1" s="4">
+      <c r="AF1" s="3">
         <v>2050</v>
       </c>
-      <c r="AF1" s="1"/>
       <c r="AG1" s="1"/>
       <c r="AH1" s="1"/>
+      <c r="AI1" s="1"/>
     </row>
-    <row r="2" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:35" ht="13.9" x14ac:dyDescent="0.35">
+      <c r="A2" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="2">
-        <v>0</v>
-      </c>
-      <c r="D2" s="2">
-        <v>0</v>
-      </c>
-      <c r="E2" s="2">
-        <v>0</v>
-      </c>
-      <c r="F2" s="2">
-        <v>0</v>
-      </c>
-      <c r="G2" s="2">
-        <v>0</v>
-      </c>
-      <c r="H2" s="2">
-        <v>0</v>
-      </c>
-      <c r="I2" s="2">
-        <v>0</v>
-      </c>
-      <c r="J2" s="2">
-        <v>0</v>
-      </c>
-      <c r="K2" s="2">
-        <v>0</v>
-      </c>
-      <c r="L2" s="2">
-        <v>0</v>
-      </c>
-      <c r="M2" s="2">
-        <v>0</v>
-      </c>
-      <c r="N2" s="2">
-        <v>0</v>
-      </c>
-      <c r="O2" s="2">
-        <v>0</v>
-      </c>
-      <c r="P2" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="2">
-        <v>0</v>
-      </c>
-      <c r="R2" s="2">
-        <v>0</v>
-      </c>
-      <c r="S2" s="2">
-        <v>0</v>
-      </c>
-      <c r="T2" s="2">
-        <v>0</v>
-      </c>
-      <c r="U2" s="2">
-        <v>0</v>
-      </c>
-      <c r="V2" s="2">
-        <v>0</v>
-      </c>
-      <c r="W2" s="2">
-        <v>0</v>
-      </c>
-      <c r="X2" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y2" s="2">
-        <v>0</v>
-      </c>
-      <c r="Z2" s="2">
-        <v>0</v>
-      </c>
-      <c r="AA2" s="2">
-        <v>0</v>
-      </c>
-      <c r="AB2" s="2">
-        <v>0</v>
-      </c>
-      <c r="AC2" s="2">
-        <v>0</v>
-      </c>
-      <c r="AD2" s="2">
-        <v>0</v>
-      </c>
-      <c r="AE2" s="2">
-        <v>0</v>
-      </c>
-      <c r="AF2" s="2"/>
+      <c r="C2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="5">
+        <v>0</v>
+      </c>
+      <c r="E2" s="5">
+        <v>0</v>
+      </c>
+      <c r="F2" s="5">
+        <v>0</v>
+      </c>
+      <c r="G2" s="5">
+        <v>0</v>
+      </c>
+      <c r="H2" s="5">
+        <v>0</v>
+      </c>
+      <c r="I2" s="5">
+        <v>0</v>
+      </c>
+      <c r="J2" s="5">
+        <v>0</v>
+      </c>
+      <c r="K2" s="5">
+        <v>0</v>
+      </c>
+      <c r="L2" s="5">
+        <v>0</v>
+      </c>
+      <c r="M2" s="5">
+        <v>0</v>
+      </c>
+      <c r="N2" s="5">
+        <v>0</v>
+      </c>
+      <c r="O2" s="5">
+        <v>0</v>
+      </c>
+      <c r="P2" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="5">
+        <v>0</v>
+      </c>
+      <c r="R2" s="5">
+        <v>0</v>
+      </c>
+      <c r="S2" s="5">
+        <v>0</v>
+      </c>
+      <c r="T2" s="5">
+        <v>0</v>
+      </c>
+      <c r="U2" s="5">
+        <v>0</v>
+      </c>
+      <c r="V2" s="5">
+        <v>0</v>
+      </c>
+      <c r="W2" s="5">
+        <v>0</v>
+      </c>
+      <c r="X2" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y2" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z2" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA2" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB2" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC2" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD2" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE2" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF2" s="5">
+        <v>0</v>
+      </c>
       <c r="AG2" s="2"/>
       <c r="AH2" s="2"/>
+      <c r="AI2" s="2"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD59F9B0-08E1-46BB-9EFF-C5155DD4B235}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:1" ht="83.65" x14ac:dyDescent="6.65">
+      <c r="A1" s="6" t="s">
+        <v>4</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
